--- a/Tagihan/2026/Juli/Doni AC.xlsx
+++ b/Tagihan/2026/Juli/Doni AC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Data Pekerjaan\Tagihan\2026\Juli\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9448B21A-E358-45F7-B1BD-925F7A0FE316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F54A639-974A-4497-B965-037479D15F7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -105,8 +105,23 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
+    <t>Camera Proview FC Audio</t>
+  </si>
+  <si>
+    <t>Pcs</t>
+  </si>
+  <si>
+    <t>Konektor BNC</t>
+  </si>
+  <si>
+    <t>Kabel CCTV Outdoor</t>
+  </si>
+  <si>
+    <t>Mtr</t>
+  </si>
+  <si>
     <r>
-      <t>Tanjung, 27</t>
+      <t>Tanjung,</t>
     </r>
     <r>
       <rPr>
@@ -116,7 +131,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve"> Juni</t>
+      <t xml:space="preserve"> 27 Juni</t>
     </r>
     <r>
       <rPr>
@@ -137,21 +152,6 @@
       </rPr>
       <t>2026</t>
     </r>
-  </si>
-  <si>
-    <t>Camera Proview FC Audio</t>
-  </si>
-  <si>
-    <t>Pcs</t>
-  </si>
-  <si>
-    <t>Konektor BNC</t>
-  </si>
-  <si>
-    <t>Kabel CCTV Outdoor</t>
-  </si>
-  <si>
-    <t>Mtr</t>
   </si>
 </sst>
 </file>
@@ -1100,7 +1100,7 @@
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="49" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G13" s="49"/>
       <c r="N13" s="6" t="s">
@@ -1146,13 +1146,13 @@
         <v>1</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D17" s="14">
         <v>5</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F17" s="27">
         <v>300000</v>
@@ -1167,13 +1167,13 @@
         <v>2</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D18" s="2">
         <v>20</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F18" s="29">
         <v>5000</v>
@@ -1188,13 +1188,13 @@
         <v>3</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D19" s="2">
         <v>48</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F19" s="29">
         <v>4000</v>
